--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.67 ± 0.06</t>
+          <t>0.65 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.56 ± 0.06</t>
+          <t>0.54 ± 0.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.16</t>
+          <t>0.48 ± 0.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.16</t>
+          <t>0.67 ± 0.18</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.73 ± 0.17</t>
+          <t>0.70 ± 0.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.65 ± 0.19</t>
+          <t>0.54 ± 0.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F4" t="n">
